--- a/docs/sample_priority_list.xlsx
+++ b/docs/sample_priority_list.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lines" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lines" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Method" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lines'!$A$1:$W$83</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -53,7 +56,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -470,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20,050 ledger lines; 7,293 meet at least one test</t>
+          <t>20,050 ledger lines; 7,275 meet at least one test</t>
         </is>
       </c>
     </row>
@@ -482,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Partial: the top 82 of 7,293 flagged lines by score. One row per ledger line, not per voucher.</t>
+          <t>Partial: the top 82 of 7,275 flagged lines by score. One row per ledger line, not per voucher.</t>
         </is>
       </c>
     </row>
@@ -513,146 +516,182 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parameter: Weekend days</t>
+          <t>Parameter: Financial year-end</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saturday, Sunday</t>
+          <t>End of December</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameter: Financial year-end</t>
+          <t>Parameter: Weekend days</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31 December</t>
+          <t>Saturday, Sunday</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Parameter: Period-end windows</t>
+          <t>Parameter: Public holidays</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>last 3 and first 2 days of each quarter; 5 working days either side of the year-end</t>
+          <t>AE calendar (holidays package 0.106)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Parameter: Weekend, holiday and round-amount tests</t>
+          <t>Parameter: Manual entries</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>manual lines only</t>
+          <t>Source is Manual (case ignored)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Parameter: Round amount</t>
+          <t>Parameter: Seldom-used account</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>multiple of 10,000</t>
+          <t>3 entries or fewer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parameter: Seldom-used account</t>
+          <t>Parameter: Large amount</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3 entries or fewer</t>
+          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Parameter: Keywords</t>
+          <t>Parameter: Period-end windows</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
+          <t>last 3 and first 2 days of each quarter; 5 working days either side of the year-end</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parameter: Generic narration words</t>
+          <t>Parameter: Weekend, holiday and round-amount tests</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
+          <t>manual lines only</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Parameter: List size</t>
+          <t>Parameter: Round amount</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.577 x square root of the ledger lines, within 20-150</t>
+          <t>multiple of 10,000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Date run (UTC)</t>
+          <t>Parameter: Keywords</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prepared by</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>Parameter: Generic narration words</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reviewed by</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>Parameter: List size</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.577 x square root of the ledger lines, within 20-150</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Date run (UTC)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Prepared by</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Reviewed by</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>See the Method sheet. Internal to the audit team: not for the client.</t>
         </is>
@@ -669,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T83"/>
+  <dimension ref="A1:W83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -684,14 +723,17 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="70" customWidth="1" min="13" max="13"/>
-    <col width="70" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,40 +799,55 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Period-End Window</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Narration Issue</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>Why Selected</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Score Breakdown</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Selected</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Planned risk</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Work done</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Evidence ref</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Tested by / date</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Auditor's conclusion</t>
         </is>
@@ -845,24 +902,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.944</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>56.99</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>related party</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Description matches the keyword list; a round amount; a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer; a large amount (29 times the median).</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.47</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.48</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,24 +977,27 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.858</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>51.897</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer; a large amount (45 times the median).</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.67</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,24 +1048,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.686</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>48.728</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>related party</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Posted on a Saturday; description matches the keyword list; a manual entry; first digit over-represented in this ledger (Benford); created and approved by the same user ID; posted to an account with 3 entries or fewer; a large amount (20 times the median).</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + Keyword Match 3.6 + date (Saturday) 1.4 + Manual Entry 0.8 + Benford 0.5, × amount 2.31</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1049,24 +1123,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>42.226</v>
+        <v>43.133</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Posted near a quarter end; an amount ending in 99 or 999; created and approved by the same user ID; posted to an account with 3 entries or fewer; a large amount (12 times the median).</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + Ending 99/999 4.0 + date (Period End) 1.1, × amount 2.12</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + Ending 99/999 4.4 + date (Period End) 1.1, × amount 2.13</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1117,24 +1198,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.079</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>42.111</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Numbers only</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Posted on a Saturday; a round amount; no or vague narration; a manual entry; created and approved by the same user ID; a large amount (41 times the median).</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Rounded Amount 3.8 + No or Vague Narration 2.5 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 2.62</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Rounded Amount 3.8 + No or Vague Narration 2.5 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 2.63</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1185,24 +1273,35 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>40.347</v>
+        <v>41.41</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>Posted just after the prior year-end; description matches the keyword list; an amount ending in 99 or 999; posted to an account with 3 entries or fewer; a large amount (33 times the median).</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0 + Keyword Match 3.6 + date (Period End) 1.1, × amount 2.52</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4 + Keyword Match 3.6 + date (Period End) 1.1, × amount 2.53</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1253,45 +1352,52 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40.034</v>
+        <v>41.173</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Too short</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Posted near a quarter end; an amount ending in 99 or 999; no or vague narration; posted to an account with 3 entries or fewer; a large amount (47 times the median).</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 2.68</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 2.68</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15977</v>
+        <v>17217</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>45947</v>
+        <v>45970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Suspense Account 35</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Write off - settlement</t>
-        </is>
-      </c>
+          <t>Suspense Account 46</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1313,49 +1419,60 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>80000</v>
+        <v>49999</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Keyword Match, Rounded Amount, Manual Entry, Seldom Account Entries</t>
+          <t>Ending 99/999, No or Vague Narration, Sunday, Manual Entry, Benford, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>39.385</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a round amount; a manual entry; posted to an account with 3 entries or fewer; a large amount (33 times the median).</t>
-        </is>
-      </c>
+        <v>39.551</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.4 + Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.53</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Posted on a Sunday; an amount ending in 99 or 999; no or vague narration; a manual entry; first digit over-represented in this ledger (Benford); posted to an account with 3 entries or fewer; a large amount (21 times the median).</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4 + No or Vague Narration 2.5 + date (Sunday) 1.4 + Manual Entry 0.8 + Benford 0.5, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17217</v>
+        <v>15977</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>45970</v>
+        <v>45947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Suspense Account 46</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Suspense Account 35</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Write off - settlement</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1377,32 +1494,39 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>49999</v>
+        <v>80000</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ending 99/999, No or Vague Narration, Sunday, Manual Entry, Benford, Seldom Account Entries</t>
+          <t>Keyword Match, Rounded Amount, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.565</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; an amount ending in 99 or 999; no or vague narration; a manual entry; first digit over-represented in this ledger (Benford); posted to an account with 3 entries or fewer; a large amount (21 times the median).</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0 + No or Vague Narration 2.5 + date (Sunday) 1.4 + Manual Entry 0.8 + Benford 0.5, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+        <v>39.431</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>settlement, write off</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a round amount; a manual entry; posted to an account with 3 entries or fewer; a large amount (33 times the median).</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.53</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1453,24 +1577,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.512</v>
+        <v>37.639</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Posted just after the prior year-end and on a Sunday; an amount ending in 99 or 999; a manual entry; posted to an account with 3 entries or fewer; a large amount (49 times the median).</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.69</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.70</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1521,24 +1652,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.142</v>
+        <v>36.169</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Posted just after the prior year-end and on a Sunday; a round amount; a manual entry; posted to an account with 3 entries or fewer; a large amount (49 times the median).</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+          <t>Opening cut-off</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Posted just after the prior year-end and on a Sunday; a round amount; a manual entry; posted to an account with 3 entries or fewer; a large amount (50 times the median).</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Seldom Account Entries 7.4 + Rounded Amount 3.8 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.70</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1589,24 +1727,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.494</v>
+        <v>35.527</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>Posted near the year-end; a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer; a large amount (12 times the median).</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Seldom Account Entries 7.4 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.13</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1657,24 +1802,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.246</v>
-      </c>
-      <c r="M14" t="inlineStr">
+        <v>35.276</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>A round amount; no or vague narration; a manual entry; created and approved by the same user ID; a large amount (25 times the median).</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Rounded Amount 3.8 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.41</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1725,24 +1877,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.272</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a manual entry; posted to an account with 3 entries or fewer; a large amount (67 times the median).</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.83</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>33.295</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a manual entry; posted to an account with 3 entries or fewer; a large amount (68 times the median).</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.84</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1793,24 +1952,35 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.578</v>
+        <v>32.602</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>Posted near the year-end; description matches the keyword list; created and approved by the same user ID; a large amount (49 times the median).</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Keyword Match 3.6 + date (Period End) 1.1, × amount 2.70</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1861,24 +2031,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.499</v>
-      </c>
-      <c r="M17" t="inlineStr">
+        <v>31.531</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Posted on a Saturday; a round amount; no or vague narration; a manual entry; created and approved by the same user ID.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Rounded Amount 3.8 + No or Vague Narration 2.5 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 1.97</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1929,24 +2106,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.485</v>
-      </c>
-      <c r="M18" t="inlineStr">
+        <v>31.511</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>related party</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Posted on a Saturday; description matches the keyword list; a manual entry; created and approved by the same user ID; a large amount (23 times the median).</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Keyword Match 3.6 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 2.38</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1997,24 +2181,35 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.149</v>
+        <v>31.171</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Numbers only</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>Posted near a quarter end; no or vague narration; created and approved by the same user ID; a large amount (66 times the median).</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 2.82</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 2.83</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2065,24 +2260,31 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>30.784</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>30.815</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Description matches the keyword list; a round amount; a manual entry; created and approved by the same user ID.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.97</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2133,45 +2335,48 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>29.423</v>
-      </c>
-      <c r="M21" t="inlineStr">
+        <v>30.426</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>An amount ending in 99 or 999; a manual entry; created and approved by the same user ID; a large amount (24 times the median).</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Ending 99/999 4.0 + Manual Entry 0.8, × amount 2.40</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Ending 99/999 4.4 + Manual Entry 0.8, × amount 2.40</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>15733</v>
+        <v>8938</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>45944</v>
+        <v>45823</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Suspense Account 34</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2193,53 +2398,60 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>50000</v>
+        <v>162999</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Rounded Amount, Manual Entry, Seldom Account Entries</t>
+          <t>Keyword Match, Ending 99/999, Sunday, Manual Entry</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>28.029</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry; posted to an account with 3 entries or fewer; a large amount (21 times the median).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>28.812</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>cash advance, no invoice</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Posted on a Sunday; description matches the keyword list; an amount ending in 99 or 999; a manual entry; a large amount (67 times the median).</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.83</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8938</v>
+        <v>15733</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45823</v>
+        <v>45944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Suspense Account 34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2261,32 +2473,35 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>162999</v>
+        <v>50000</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Keyword Match, Ending 99/999, Sunday, Manual Entry</t>
+          <t>Rounded Amount, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>27.636</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; description matches the keyword list; an amount ending in 99 or 999; a manual entry; a large amount (67 times the median).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.83</t>
-        </is>
-      </c>
+        <v>28.053</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A round amount; a manual entry; posted to an account with 3 entries or fewer; a large amount (21 times the median).</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2337,50 +2552,57 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>26.604</v>
-      </c>
-      <c r="M24" t="inlineStr">
+        <v>26.635</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Description matches the keyword list; a round amount; a manual entry; posted to an account with 3 entries or fewer.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Seldom Account Entries 7.4 + Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.71</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19895</v>
+        <v>5588</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46021</v>
+        <v>45762</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Suspense Account 33</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2394,56 +2616,59 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>22732.61</v>
+        <v>27999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Keyword Match, Period End, Same User Created and Approved</t>
+          <t>Ending 99/999, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>24.331</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; description matches the keyword list; created and approved by the same user ID.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Keyword Match 3.6 + date (Period End) 1.1, × amount 2.02</t>
-        </is>
-      </c>
+        <v>24.7</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>An amount ending in 99 or 999; posted to an account with 3 entries or fewer; a large amount (12 times the median).</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4, × amount 2.10</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5588</v>
+        <v>837</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>45762</v>
+        <v>45673</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Suspense Account 33</t>
+          <t>Suspense Account 41</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>104522</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2462,61 +2687,68 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>27999</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ending 99/999, Seldom Account Entries</t>
+          <t>Ending 99/999, No or Vague Narration, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>23.821</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>An amount ending in 99 or 999; posted to an account with 3 entries or fewer; a large amount (12 times the median).</t>
-        </is>
-      </c>
+        <v>24.431</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0, × amount 2.10</t>
+          <t>Numbers only</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>An amount ending in 99 or 999; no or vague narration; posted to an account with 3 entries or fewer.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4 + No or Vague Narration 2.5, × amount 1.71</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>837</v>
+        <v>19895</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45673</v>
+        <v>46021</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Suspense Account 41</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>104522</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2530,61 +2762,72 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>22732.61</v>
       </c>
       <c r="J27" t="n">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ending 99/999, No or Vague Narration, Seldom Account Entries</t>
+          <t>Keyword Match, Period End, Same User Created and Approved</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>23.706</v>
+        <v>24.355</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>An amount ending in 99 or 999; no or vague narration; posted to an account with 3 entries or fewer.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0 + No or Vague Narration 2.5, × amount 1.71</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>cash advance, no invoice</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; description matches the keyword list; created and approved by the same user ID.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Keyword Match 3.6 + date (Period End) 1.1, × amount 2.02</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2789</v>
+        <v>12078</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45708</v>
+        <v>45880</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suspense Account 17</t>
+          <t>Suspense Account 16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Being adjustment</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2601,53 +2844,56 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>56477.62</v>
+        <v>24999</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>No or Vague Narration, Seldom Account Entries</t>
+          <t>Ending 99/999, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>23.535</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>No or vague narration; posted to an account with 3 entries or fewer; a large amount (23 times the median).</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + No or Vague Narration 2.5, × amount 2.38</t>
-        </is>
-      </c>
+        <v>24.171</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>An amount ending in 99 or 999; posted to an account with 3 entries or fewer; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4, × amount 2.06</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4188</v>
+        <v>2789</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>45735</v>
+        <v>45708</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Suspense Account 17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Correction entry - reversal</t>
+          <t>Being adjustment</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2657,55 +2903,62 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>170000</v>
+        <v>56477.62</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Keyword Match, Rounded Amount, Manual Entry</t>
+          <t>No or Vague Narration, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>23.424</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (70 times the median).</t>
-        </is>
-      </c>
+        <v>23.555</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.85</t>
+          <t>Generic words only</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>No or vague narration; posted to an account with 3 entries or fewer; a large amount (23 times the median).</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + No or Vague Narration 2.5, × amount 2.39</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9547</v>
+        <v>4188</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>45833</v>
+        <v>45735</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2715,80 +2968,87 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>29502.29</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Keyword Match, Same User Created and Approved</t>
+          <t>Keyword Match, Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>23.326</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; created and approved by the same user ID; a large amount (12 times the median).</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Keyword Match 3.6, × amount 2.12</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+        <v>23.44</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (70 times the median).</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.85</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>12078</v>
+        <v>9547</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>45880</v>
+        <v>45833</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Suspense Account 16</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2802,35 +3062,42 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>29502.29</v>
       </c>
       <c r="J31" t="n">
-        <v>24999</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Ending 99/999, Seldom Account Entries</t>
+          <t>Keyword Match, Same User Created and Approved</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>An amount ending in 99 or 999; posted to an account with 3 entries or fewer; a large amount (10 times the median).</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0, × amount 2.05</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+        <v>23.348</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; created and approved by the same user ID; a large amount (12 times the median).</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Keyword Match 3.6, × amount 2.12</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2881,31 +3148,38 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>22.815</v>
-      </c>
-      <c r="M32" t="inlineStr">
+        <v>22.838</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>settlement, write off</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Description matches the keyword list; a manual entry; posted to an account with 3 entries or fewer.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.94</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.95</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8607</v>
+        <v>19950</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>45818</v>
+        <v>46021</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2914,12 +3188,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Correction entry - reversal</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2929,44 +3203,55 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>130000</v>
+        <v>169999</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Keyword Match, Rounded Amount, Manual Entry</t>
+          <t>Ending 99/999, No or Vague Narration, Period End</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>22.479</v>
+        <v>22.81</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (53 times the median).</t>
+          <t>Year end</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.74</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; an amount ending in 99 or 999; no or vague narration; a large amount (70 times the median).</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 2.85</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3017,103 +3302,113 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>21.856</v>
-      </c>
-      <c r="M34" t="inlineStr">
+        <v>22.665</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>An amount ending in 99 or 999; posted to an account with 3 entries or fewer.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + Ending 99/999 4.0, × amount 1.93</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + Ending 99/999 4.4, × amount 1.93</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13429</v>
+        <v>8607</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>45903</v>
+        <v>45818</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Suspense Account 20</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>35854.05</v>
+        <v>130000</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>No or Vague Narration, Seldom Account Entries</t>
+          <t>Keyword Match, Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>21.68</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>No or vague narration; posted to an account with 3 entries or fewer; a large amount (15 times the median).</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + No or Vague Narration 2.5, × amount 2.20</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+        <v>22.495</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (54 times the median).</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.74</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>19950</v>
+        <v>13429</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46021</v>
+        <v>45903</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Suspense Account 20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3123,12 +3418,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3145,53 +3440,60 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>169999</v>
+        <v>35854.05</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ending 99/999, No or Vague Narration, Period End</t>
+          <t>No or Vague Narration, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>21.631</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; an amount ending in 99 or 999; no or vague narration; a large amount (70 times the median).</t>
-        </is>
-      </c>
+        <v>21.7</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.0 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 2.85</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>No or vague narration; posted to an account with 3 entries or fewer; a large amount (15 times the median).</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + No or Vague Narration 2.5, × amount 2.20</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15624</v>
+        <v>18719</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45942</v>
+        <v>45999</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Suspense Account 43</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3201,70 +3503,77 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>33134.34</v>
+        <v>92999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Sunday, Manual Entry, Seldom Account Entries</t>
+          <t>Keyword Match, Ending 99/999</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>20.665</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; a manual entry; posted to an account with 3 entries or fewer; a large amount (14 times the median).</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.17</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+        <v>20.688</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; an amount ending in 99 or 999; a large amount (38 times the median).</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + Keyword Match 3.6, × amount 2.60</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>8919</v>
+        <v>15624</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>45821</v>
+        <v>45942</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Suspense Account 43</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Adj</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3278,51 +3587,54 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>33134.34</v>
       </c>
       <c r="J38" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Rounded Amount, No or Vague Narration, Manual Entry</t>
+          <t>Sunday, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>20.628</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>A round amount; no or vague narration; a manual entry; a large amount (74 times the median).</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.88</t>
-        </is>
-      </c>
+        <v>20.684</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Posted on a Sunday; a manual entry; posted to an account with 3 entries or fewer; a large amount (14 times the median).</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.17</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>334</v>
+        <v>8919</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45664</v>
+        <v>45821</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Adj</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3332,138 +3644,156 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>15464.86</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>No or Vague Narration, Period End, Same User Created and Approved</t>
+          <t>Rounded Amount, No or Vague Narration, Manual Entry</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Posted just after the prior year-end; no or vague narration; created and approved by the same user ID.</t>
-        </is>
-      </c>
+        <v>20.65</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.5 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 1.87</t>
+          <t>Generic words only</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A round amount; no or vague narration; a manual entry; a large amount (74 times the median).</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.88</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11122</v>
+        <v>334</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45861</v>
+        <v>45664</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>60000</v>
+        <v>15464.86</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Keyword Match, Rounded Amount, Manual Entry</t>
+          <t>No or Vague Narration, Period End, Same User Created and Approved</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>19.801</v>
+        <v>20.623</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (25 times the median).</t>
+          <t>Opening cut-off</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.41</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Posted just after the prior year-end; no or vague narration; created and approved by the same user ID.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 1.87</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18719</v>
+        <v>11122</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45999</v>
+        <v>45861</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Correction entry - reversal</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3473,44 +3803,51 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>92999</v>
+        <v>60000</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Keyword Match, Ending 99/999</t>
+          <t>Keyword Match, Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>19.613</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; an amount ending in 99 or 999; a large amount (38 times the median).</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + Keyword Match 3.6, × amount 2.59</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+        <v>19.817</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>settlement, write off</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (25 times the median).</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.41</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3561,24 +3898,35 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>19.505</v>
+        <v>19.523</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Posted just after the prior year-end; a round amount; no or vague narration; a manual entry; first digit over-represented in this ledger (Benford); a large amount (16 times the median).</t>
+          <t>Opening cut-off</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
+          <t>Generic words only</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Posted just after the prior year-end; a round amount; no or vague narration; a manual entry; first digit over-represented in this ledger (Benford); a large amount (17 times the median).</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>Rounded Amount 3.8 + No or Vague Narration 2.5 + date (Period End) 1.1 + Manual Entry 0.8 + Benford 0.5, × amount 2.24</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3629,24 +3977,35 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>19.21</v>
+        <v>19.221</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Generic words only</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
           <t>Posted near a quarter end; no or vague narration; created and approved by the same user ID.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5 + No or Vague Narration 2.5 + date (Period End) 1.1, × amount 1.74</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3697,176 +4056,189 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>18.905</v>
-      </c>
-      <c r="M44" t="inlineStr">
+        <v>18.925</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>Posted on a Saturday; description matches the keyword list; a round amount; a manual entry.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Rounded Amount 3.8 + Keyword Match 3.6 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 1.97</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>15304</v>
+        <v>2903</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45936</v>
+        <v>45710</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Suspense Account 22</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>69414.87</v>
+        <v>140999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Seldom Account Entries</t>
+          <t>Ending 99/999, Saturday, Manual Entry</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>18.164</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Posted to an account with 3 entries or fewer; a large amount (29 times the median).</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.4, × amount 2.47</t>
-        </is>
-      </c>
+        <v>18.421</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Posted on a Saturday; an amount ending in 99 or 999; a manual entry; a large amount (58 times the median).</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 2.77</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15620</v>
+        <v>15304</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45941</v>
+        <v>45936</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Suspense Account 22</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>69414.87</v>
       </c>
       <c r="J46" t="n">
-        <v>15175.4</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Saturday, Manual Entry, Same User Created and Approved</t>
+          <t>Seldom Account Entries</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>18.009</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Posted on a Saturday; a manual entry; created and approved by the same user ID.</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 1.86</t>
-        </is>
-      </c>
+        <v>18.179</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Posted to an account with 3 entries or fewer; a large amount (29 times the median).</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.4, × amount 2.47</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5111</v>
+        <v>15620</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45754</v>
+        <v>45941</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3876,7 +4248,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3890,178 +4262,199 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>15175.4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Keyword Match, Rounded Amount, Manual Entry</t>
+          <t>Saturday, Manual Entry, Same User Created and Approved</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>17.459</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (12 times the median).</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.12</t>
-        </is>
-      </c>
+        <v>18.028</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Posted on a Saturday; a manual entry; created and approved by the same user ID.</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 1.86</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2903</v>
+        <v>20025</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45710</v>
+        <v>46022</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>140999</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>18999</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ending 99/999, Saturday, Manual Entry</t>
+          <t>Keyword Match, Ending 99/999, Period End</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>17.277</v>
+        <v>17.593</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Posted on a Saturday; an amount ending in 99 or 999; a manual entry; a large amount (58 times the median).</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 2.77</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; description matches the keyword list; an amount ending in 99 or 999.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + Keyword Match 3.6 + date (Period End) 1.1, × amount 1.95</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>216</v>
+        <v>5111</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45660</v>
+        <v>45754</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>20388.24</v>
+        <v>30000</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Period End, Same User Created and Approved</t>
+          <t>Keyword Match, Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>16.804</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Posted just after the prior year-end; created and approved by the same user ID.</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + date (Period End) 1.1, × amount 1.97</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+        <v>17.475</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a round amount; a manual entry; a large amount (12 times the median).</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.13</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20025</v>
+        <v>6022</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46022</v>
+        <v>45770</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4075,12 +4468,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4094,56 +4487,63 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>30999</v>
       </c>
       <c r="J50" t="n">
-        <v>18999</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Keyword Match, Ending 99/999, Period End</t>
+          <t>Keyword Match, Ending 99/999</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>16.781</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; description matches the keyword list; an amount ending in 99 or 999.</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + Keyword Match 3.6 + date (Period End) 1.1, × amount 1.95</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+        <v>17.054</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; an amount ending in 99 or 999; a large amount (13 times the median).</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + Keyword Match 3.6, × amount 2.14</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17588</v>
+        <v>7730</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45975</v>
+        <v>45802</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4153,70 +4553,73 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>88999</v>
       </c>
       <c r="J51" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Keyword Match, Duplicate</t>
+          <t>Ending 99/999, Sunday, Manual Entry</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>16.364</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; same date, account, description and amount as another line; a large amount (21 times the median).</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Keyword Match 3.6 + Duplicate 3.5, × amount 2.33</t>
-        </is>
-      </c>
+        <v>17.028</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Posted on a Sunday; an amount ending in 99 or 999; a manual entry; a large amount (37 times the median).</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.58</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>17599</v>
+        <v>216</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45975</v>
+        <v>45660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4230,42 +4633,49 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>20388.24</v>
       </c>
       <c r="J52" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Keyword Match, Duplicate</t>
+          <t>Period End, Same User Created and Approved</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>16.364</v>
+        <v>16.821</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Description matches the keyword list; same date, account, description and amount as another line; a large amount (21 times the median).</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Keyword Match 3.6 + Duplicate 3.5, × amount 2.33</t>
-        </is>
-      </c>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Posted just after the prior year-end; created and approved by the same user ID.</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + date (Period End) 1.1, × amount 1.98</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6022</v>
+        <v>17588</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45770</v>
+        <v>45975</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4274,12 +4684,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Director fees</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4298,42 +4708,49 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>30999</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Keyword Match, Ending 99/999</t>
+          <t>Keyword Match, Duplicate</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>16.173</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; an amount ending in 99 or 999; a large amount (13 times the median).</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + Keyword Match 3.6, × amount 2.14</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+        <v>16.378</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; same date, account, description and amount as another line; a large amount (21 times the median).</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + Duplicate 3.5, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1927</v>
+        <v>17599</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45692</v>
+        <v>45975</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4347,7 +4764,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4357,70 +4774,77 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Keyword Match, Rounded Amount, Manual Entry</t>
+          <t>Keyword Match, Duplicate</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>16.144</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a round amount; a manual entry.</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.97</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+        <v>16.378</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; same date, account, description and amount as another line; a large amount (21 times the median).</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + Duplicate 3.5, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6971</v>
+        <v>1927</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45788</v>
+        <v>45692</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Director fees</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4437,39 +4861,46 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>144789.73</v>
+        <v>20000</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Keyword Match, Sunday, Manual Entry</t>
+          <t>Keyword Match, Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>16.002</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; description matches the keyword list; a manual entry; a large amount (60 times the median).</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.78</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+        <v>16.161</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; a round amount; a manual entry.</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.97</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7730</v>
+        <v>6971</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45802</v>
+        <v>45788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4478,17 +4909,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4502,187 +4933,204 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>88999</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>144789.73</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Ending 99/999, Sunday, Manual Entry</t>
+          <t>Keyword Match, Sunday, Manual Entry</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>15.957</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; an amount ending in 99 or 999; a manual entry; a large amount (37 times the median).</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.58</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+        <v>16.014</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Posted on a Sunday; description matches the keyword list; a manual entry; a large amount (60 times the median).</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.78</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13183</v>
+        <v>1496</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45898</v>
+        <v>45685</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>17028.02</v>
+        <v>20999</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Manual Entry, Same User Created and Approved</t>
+          <t>Keyword Match, Ending 99/999</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>15.751</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>A manual entry; created and approved by the same user ID.</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.5 + Manual Entry 0.8, × amount 1.90</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+        <v>15.826</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>settlement, write off</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Description matches the keyword list; an amount ending in 99 or 999.</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + Keyword Match 3.6, × amount 1.99</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1496</v>
+        <v>13183</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>45685</v>
+        <v>45898</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>20999</v>
+        <v>17028.02</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Keyword Match, Ending 99/999</t>
+          <t>Manual Entry, Same User Created and Approved</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>15.001</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; an amount ending in 99 or 999.</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + Keyword Match 3.6, × amount 1.98</t>
-        </is>
-      </c>
+        <v>15.768</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>A manual entry; created and approved by the same user ID.</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.5 + Manual Entry 0.8, × amount 1.91</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4693</v>
+        <v>4697</v>
       </c>
       <c r="B59" s="1" t="n">
         <v>45746</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4692,65 +5140,72 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>176999</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Rounded Amount, Period End, Public Holiday, Sunday, Manual Entry</t>
+          <t>Ending 99/999, Period End</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>14.906</v>
+        <v>15.722</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Posted near a quarter end and on a public holiday and on a Sunday; a round amount; a manual entry; a large amount (29 times the median).</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.47</t>
-        </is>
-      </c>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Posted near a quarter end; an amount ending in 99 or 999; a large amount (73 times the median).</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.4 + date (Period End) 1.1, × amount 2.87</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4697</v>
+        <v>4693</v>
       </c>
       <c r="B60" s="1" t="n">
         <v>45746</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4760,49 +5215,56 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="J60" t="n">
-        <v>176999</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Ending 99/999, Period End</t>
+          <t>Rounded Amount, Period End, Public Holiday, Sunday, Manual Entry</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>14.541</v>
+        <v>14.918</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Posted near a quarter end; an amount ending in 99 or 999; a large amount (73 times the median).</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + date (Period End) 1.1, × amount 2.87</t>
-        </is>
-      </c>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Posted near a quarter end and on a public holiday and on a Sunday; a round amount; a manual entry; a large amount (29 times the median).</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.48</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4853,24 +5315,27 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>14.535</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; a round amount; a manual entry; first digit over-represented in this ledger (Benford); a large amount (16 times the median).</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
+        <v>14.548</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Posted on a Sunday; a round amount; a manual entry; first digit over-represented in this ledger (Benford); a large amount (17 times the median).</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Rounded Amount 3.8 + date (Sunday) 1.4 + Manual Entry 0.8 + Benford 0.5, × amount 2.24</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4921,24 +5386,27 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>14.364</v>
-      </c>
-      <c r="M62" t="inlineStr">
+        <v>14.378</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
         <is>
           <t>Created and approved by the same user ID.</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Same User Created and Approved 7.5, × amount 1.93</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4989,24 +5457,31 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>13.862</v>
+        <v>13.875</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Posted near the year-end; a round amount; a manual entry; first digit over-represented in this ledger (Benford); a large amount (16 times the median).</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; a round amount; a manual entry; first digit over-represented in this ledger (Benford); a large amount (17 times the median).</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Rounded Amount 3.8 + date (Period End) 1.1 + Manual Entry 0.8 + Benford 0.5, × amount 2.24</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5057,24 +5532,31 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>13.362</v>
+        <v>13.374</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
           <t>Posted just after the prior year-end; a round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5125,24 +5607,35 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>13.237</v>
+        <v>13.248</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
           <t>Posted just after the prior year-end; description matches the keyword list; a manual entry; a large amount (26 times the median).</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Keyword Match 3.6 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.43</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5193,24 +5686,27 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>12.893</v>
-      </c>
-      <c r="M66" t="inlineStr">
+        <v>12.903</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (58 times the median).</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.77</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5261,24 +5757,27 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>12.586</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry; a large amount (49 times the median).</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
+        <v>12.595</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>A round amount; a manual entry; a large amount (50 times the median).</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.70</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5329,50 +5828,57 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>12.585</v>
-      </c>
-      <c r="M68" t="inlineStr">
+        <v>12.594</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Numbers only</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
         <is>
           <t>Posted on a Saturday; no or vague narration; a manual entry; a large amount (44 times the median).</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>No or Vague Narration 2.5 + date (Saturday) 1.4 + Manual Entry 0.8, × amount 2.65</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5324</v>
+        <v>4887</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>45756</v>
+        <v>45749</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VAT Payable</t>
+          <t>Rent Expense</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5386,51 +5892,58 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>47899.39</v>
+        <v>30000</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ending 99/999, Manual Entry, Benford</t>
+          <t>Rounded Amount, Period End, Manual Entry</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>12.247</v>
+        <v>12.177</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>An amount ending in 99 or 999; a manual entry; first digit over-represented in this ledger (Benford); a large amount (20 times the median).</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Ending 99/999 4.0 + Manual Entry 0.8 + Benford 0.5, × amount 2.32</t>
-        </is>
-      </c>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Posted near a quarter end; a round amount; a manual entry; a large amount (12 times the median).</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.13</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4887</v>
+        <v>19825</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45749</v>
+        <v>46020</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rent Expense</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5440,7 +5953,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5454,42 +5967,53 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>30000</v>
+        <v>33796.27</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Rounded Amount, Period End, Manual Entry</t>
+          <t>Keyword Match, Period End, Manual Entry</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>12.166</v>
+        <v>11.858</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Posted near a quarter end; a round amount; a manual entry; a large amount (12 times the median).</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.12</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>correction, reversal</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; description matches the keyword list; a manual entry; a large amount (14 times the median).</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.17</t>
+        </is>
+      </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>19825</v>
+        <v>19701</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46020</v>
+        <v>46016</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5498,66 +6022,77 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Correction entry - reversal</t>
+          <t>Director fees</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>33796.27</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>47950.12</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Keyword Match, Period End, Manual Entry</t>
+          <t>Keyword Match, Period End, Benford</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>11.847</v>
+        <v>11.787</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Posted near the year-end; description matches the keyword list; a manual entry; a large amount (14 times the median).</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Keyword Match 3.6 + date (Period End) 1.1 + Manual Entry 0.8, × amount 2.17</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; description matches the keyword list; first digit over-represented in this ledger (Benford); a large amount (20 times the median).</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Period End) 1.1 + Benford 0.5, × amount 2.32</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>19701</v>
+        <v>4860</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46016</v>
+        <v>45748</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5566,12 +6101,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5581,65 +6116,72 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J72" t="n">
-        <v>47950.12</v>
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Keyword Match, Period End, Benford</t>
+          <t>Rounded Amount, Period End, Public Holiday, Manual Entry</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>11.777</v>
+        <v>11.318</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Posted near the year-end; description matches the keyword list; first digit over-represented in this ledger (Benford); a large amount (20 times the median).</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Keyword Match 3.6 + date (Period End) 1.1 + Benford 0.5, × amount 2.32</t>
-        </is>
-      </c>
+          <t>Quarter end</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Posted near a quarter end and on a public holiday; a round amount; a manual entry.</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + date (Public Holiday) 1.1 + Manual Entry 0.8, × amount 1.97</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4860</v>
+        <v>17490</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>45748</v>
+        <v>45974</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5658,124 +6200,138 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Rounded Amount, Period End, Public Holiday, Manual Entry</t>
+          <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>11.307</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Posted near a quarter end and on a public holiday; a round amount; a manual entry.</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + date (Public Holiday) 1.1 + Manual Entry 0.8, × amount 1.97</t>
-        </is>
-      </c>
+        <v>11.235</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>A round amount; a manual entry; a large amount (25 times the median).</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.41</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>17490</v>
+        <v>19726</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>45974</v>
+        <v>46016</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>60000</v>
+        <v>62539.64</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Rounded Amount, Manual Entry</t>
+          <t>Keyword Match, Period End</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>11.226</v>
+        <v>11.234</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>A round amount; a manual entry; a large amount (25 times the median).</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.41</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>related party</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Posted near the year-end; description matches the keyword list; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Period End) 1.1, × amount 2.43</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>19726</v>
+        <v>2361</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46016</v>
+        <v>45700</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>VAT Payable</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Consultancy fee (related party)</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5785,65 +6341,68 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>62539.64</v>
+        <v>50000</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Keyword Match, Period End</t>
+          <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>11.225</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; description matches the keyword list; a large amount (26 times the median).</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Keyword Match 3.6 + date (Period End) 1.1, × amount 2.43</t>
-        </is>
-      </c>
+        <v>10.881</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>A round amount; a manual entry; a large amount (21 times the median).</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2361</v>
+        <v>2581</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>45700</v>
+        <v>45705</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VAT Payable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5873,45 +6432,48 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M76" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2581</v>
+        <v>2785</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>45705</v>
+        <v>45708</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5930,10 +6492,10 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J77" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5941,35 +6503,38 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M77" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2785</v>
+        <v>3155</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>45708</v>
+        <v>45715</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5979,7 +6544,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6009,50 +6574,53 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M78" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3155</v>
+        <v>4103</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>45715</v>
+        <v>45734</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6066,46 +6634,49 @@
         </is>
       </c>
       <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
         <v>50000</v>
       </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M79" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4103</v>
+        <v>5662</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>45734</v>
+        <v>45763</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Rent Expense</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6115,7 +6686,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6134,10 +6705,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J80" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6145,31 +6716,34 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M80" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5662</v>
+        <v>5748</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6178,7 +6752,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6213,45 +6787,48 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M81" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5748</v>
+        <v>6292</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>45764</v>
+        <v>45776</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rent Expense</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6281,45 +6858,48 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M82" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>6292</v>
+        <v>11280</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>45776</v>
+        <v>45863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6338,37 +6918,41 @@
         </is>
       </c>
       <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
         <v>50000</v>
       </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>10.872</v>
-      </c>
-      <c r="M83" t="inlineStr">
+        <v>10.881</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
         <is>
           <t>A round amount; a manual entry; a large amount (21 times the median).</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.33</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.8 + Manual Entry 0.8, × amount 2.34</t>
+        </is>
+      </c>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6415,7 +6999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amount multiplier = 1 + log10(1 + amount / median), median non-zero amount 2,429.98.</t>
+          <t>Amount multiplier = 1 + log10(1 + amount / median), median non-zero amount 2,418.21.</t>
         </is>
       </c>
     </row>
@@ -6510,19 +7094,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0021</v>
+        <v>0.0011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.669</v>
+        <v>2.94</v>
       </c>
       <c r="E9" t="n">
         <v>1.5</v>
       </c>
       <c r="F9" t="n">
-        <v>4.003</v>
+        <v>4.411</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -6616,7 +7200,7 @@
         <v>0.0015</v>
       </c>
       <c r="D13" t="n">
-        <v>2.81</v>
+        <v>2.811</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -6693,7 +7277,7 @@
         <v>0.1212</v>
       </c>
       <c r="D16" t="n">
-        <v>0.916</v>
+        <v>0.917</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>

--- a/docs/sample_priority_list.xlsx
+++ b/docs/sample_priority_list.xlsx
@@ -576,72 +576,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parameter: Large amount</t>
+          <t>Parameter: Keywords</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
+          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Parameter: Period-end windows</t>
+          <t>Parameter: Generic narration words</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>last 3 and first 2 days of each quarter; 5 working days either side of the year-end</t>
+          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parameter: Weekend, holiday and round-amount tests</t>
+          <t>Parameter: Large amount</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>manual lines only</t>
+          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Parameter: Round amount</t>
+          <t>Parameter: Period-end windows</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>multiple of 10,000</t>
+          <t>last 3 and first 2 days of each quarter; 5 working days either side of the year-end</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Parameter: Keywords</t>
+          <t>Parameter: Weekend, holiday and round-amount tests</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
+          <t>manual lines only</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Parameter: Generic narration words</t>
+          <t>Parameter: Round amount</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
+          <t>multiple of 10,000</t>
         </is>
       </c>
     </row>

--- a/docs/sample_priority_list.xlsx
+++ b/docs/sample_priority_list.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -528,159 +528,163 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameter: Weekend days</t>
+          <t>Parameter: Period-end windows</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Saturday, Sunday</t>
+          <t>last 3 and first 2 days of each quarter; 5 working days either side of the year-end</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Parameter: Public holidays</t>
+          <t>Parameter: Weekend days</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AE calendar (holidays package 0.106)</t>
+          <t>Saturday, Sunday</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Parameter: Manual entries</t>
+          <t>Parameter: Public holidays</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Source is Manual (case ignored)</t>
+          <t>AE calendar (holidays package 0.106)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Parameter: Seldom-used account</t>
+          <t>Parameter: Dates</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3 entries or fewer</t>
+          <t>ambiguous dates read day first (02/03 is 2 March)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parameter: Keywords</t>
+          <t>Parameter: Manual entries</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
+          <t>Source is Manual (case ignored)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Parameter: Generic narration words</t>
+          <t>Parameter: Weekend, holiday and round-amount tests</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
+          <t>manual lines only</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parameter: Large amount</t>
+          <t>Parameter: Round amount</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
+          <t>multiple of 10,000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Parameter: Period-end windows</t>
+          <t>Parameter: Seldom-used account</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>last 3 and first 2 days of each quarter; 5 working days either side of the year-end</t>
+          <t>3 entries or fewer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Parameter: Weekend, holiday and round-amount tests</t>
+          <t>Parameter: Keywords</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>manual lines only</t>
+          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Parameter: Round amount</t>
+          <t>Parameter: Generic narration words</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>multiple of 10,000</t>
+          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parameter: List size</t>
+          <t>Parameter: Large amount</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.577 x square root of the ledger lines, within 20-150</t>
+          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Date run (UTC)</t>
+          <t>Parameter: List size</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>0.577 x square root of the ledger lines, within 20-150</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Prepared by</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Date run (UTC)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reviewed by</t>
+          <t>Prepared by</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -688,10 +692,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Reviewed by</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>See the Method sheet. Internal to the audit team: not for the client.</t>
         </is>

--- a/docs/sample_priority_list.xlsx
+++ b/docs/sample_priority_list.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ambiguous dates read day first (02/03 is 2 March)</t>
+          <t>ambiguous dates read day first (02/03 is 2 March); numbers from 20,000 to 80,000 read as Excel serial dates; time-zone offsets dropped, local time kept</t>
         </is>
       </c>
     </row>
@@ -617,82 +617,86 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3 entries or fewer</t>
+          <t>3 entries or fewer (with real IDEA exports, the threshold the macro was run with: keep it in step with SELDOM_MAX)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Parameter: Keywords</t>
+          <t>Parameter: Duplicate key</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
+          <t>Date, Account, Description and the amount</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Parameter: Generic narration words</t>
+          <t>Parameter: Keywords</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
+          <t>adjust, write off, reversal, correction, director, related party, cash advance, settlement, no invoice, suspense</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parameter: Large amount</t>
+          <t>Parameter: Generic narration words</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
+          <t>adj, adjustment, adjusting, jv, je, journal, entry, correction, reclass, misc, miscellaneous, other, general, various, sundry, test, tbd, being</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parameter: List size</t>
+          <t>Parameter: Large amount</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.577 x square root of the ledger lines, within 20-150</t>
+          <t>10 times the median non-zero amount, used in "why selected" only when performance materiality isn't set (practical judgement)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Date run (UTC)</t>
+          <t>Parameter: List size</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>0.577 x square root of the ledger lines, within 20-150</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Prepared by</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Date run (UTC)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reviewed by</t>
+          <t>Prepared by</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -700,10 +704,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Reviewed by</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>See the Method sheet. Internal to the audit team: not for the client.</t>
         </is>

--- a/docs/sample_priority_list.xlsx
+++ b/docs/sample_priority_list.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Method" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vouchers'!$A$1:$T$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vouchers'!$A$1:$U$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Lines'!$A$1:$Q$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,29 +746,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="70" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="70" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -784,90 +785,95 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Lines</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Flagged Lines</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Flagged By</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Voucher Amount</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Why Selected</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Score Breakdown</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Selected</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Planned risk</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Work done</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Evidence ref</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tested by / date</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Auditor's conclusion</t>
         </is>
@@ -882,62 +888,67 @@
           <t>JV05068</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Suspense Account 9, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>46021</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Supplier payment</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>user_c</t>
         </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Rounded Amount, Period End, Manual Entry, Same User Created and Approved, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>100000</v>
       </c>
-      <c r="L2" t="n">
-        <v>52.847</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; a round amount; a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (45 times the median).</t>
-        </is>
+      <c r="M2" t="n">
+        <v>53.939</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2 + Seldom Account Entries 7.2 + Rounded Amount 3.6 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.66</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>Posted near the year-end; a round amount; a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (51 times the median).</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Seldom Account Entries 7.2 + Rounded Amount 3.6 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.72</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -948,62 +959,67 @@
           <t>JV07030</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Suspense Account 22, Cash at Bank, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>45878</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Write off - settlement</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>user_c</t>
         </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Keyword Match, Saturday, Manual Entry, Same User Created and Approved, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>31913.42</v>
       </c>
-      <c r="L3" t="n">
-        <v>44</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Posted on a Saturday; description matches the keyword list (1 of 4 lines); a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer (1 of 4 lines); a large amount (14 times the median).</t>
-        </is>
+      <c r="M3" t="n">
+        <v>45.067</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2 + Seldom Account Entries 7.2 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 2.19</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>Posted on a Saturday; description matches the keyword list (1 of 4 lines); a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer (1 of 4 lines); a large amount (16 times the median).</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Seldom Account Entries 7.2 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 2.24</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,62 +1030,67 @@
           <t>JV07255</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Payroll Expense, VAT Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45689</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Adjustment per director</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>user_b</t>
         </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Keyword Match, Rounded Amount, Saturday, Manual Entry, Benford, Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>70000</v>
       </c>
-      <c r="L4" t="n">
-        <v>42.377</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Posted on a Saturday; description matches the keyword list (1 of 3 lines); a round amount (1 of 3 lines); a manual entry; first digit over-represented in this ledger (Benford) (1 of 3 lines); created and approved by the same user ID; a large amount (31 times the median).</t>
-        </is>
+      <c r="M4" t="n">
+        <v>43.305</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2 + Rounded Amount 3.6 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8 + Benford 0.3, × amount 2.51</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>Posted on a Saturday; description matches the keyword list (1 of 3 lines); a round amount (1 of 3 lines); a manual entry; first digit over-represented in this ledger (Benford) (1 of 3 lines); created and approved by the same user ID; a large amount (36 times the median).</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Rounded Amount 3.6 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8 + Benford 0.3, × amount 2.57</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,62 +1101,67 @@
           <t>JV04295</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Suspense Account 28, Accounts Receivable, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>45739</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Monthly payroll</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>user_d</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Ending 99/999, Sunday, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>179999</v>
       </c>
-      <c r="L5" t="n">
-        <v>40.257</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; an amount ending in 99 or 999 (1 of 3 lines); a manual entry; posted to an account with 3 entries or fewer (1 of 3 lines); a large amount (81 times the median).</t>
-        </is>
+      <c r="M5" t="n">
+        <v>41.017</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.2 + Ending 99/999 4.5 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.91</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>Posted on a Sunday; an amount ending in 99 or 999 (1 of 3 lines); a manual entry; posted to an account with 3 entries or fewer (1 of 3 lines); a large amount (92 times the median).</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + Ending 99/999 4.5 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.97</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1146,62 +1172,67 @@
           <t>JV01634</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Payroll Expense, VAT Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45798</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Write off - settlement</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>user_c</t>
         </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Keyword Match, Ending 99/999, Benford, Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>45999</v>
       </c>
-      <c r="L6" t="n">
-        <v>36.416</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list (1 of 3 lines); an amount ending in 99 or 999 (1 of 3 lines); first digit over-represented in this ledger (Benford) (1 of 3 lines); created and approved by the same user ID; a large amount (21 times the median).</t>
-        </is>
+      <c r="M6" t="n">
+        <v>37.258</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2 + Ending 99/999 4.5 + Keyword Match 3.6 + Benford 0.3, × amount 2.34</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>Description matches the keyword list (1 of 3 lines); an amount ending in 99 or 999 (1 of 3 lines); first digit over-represented in this ledger (Benford) (1 of 3 lines); created and approved by the same user ID; a large amount (24 times the median).</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Ending 99/999 4.5 + Keyword Match 3.6 + Benford 0.3, × amount 2.39</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1212,62 +1243,67 @@
           <t>JV04722</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Suspense Account 17, Accounts Payable, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45733</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Journal entry</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Rounded Amount, No or Vague Narration, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>70000</v>
       </c>
-      <c r="L7" t="n">
-        <v>35.457</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 4 lines); no or vague narration (1 of 4 lines); a manual entry; posted to an account with 3 entries or fewer (1 of 4 lines); a large amount (31 times the median).</t>
-        </is>
+      <c r="M7" t="n">
+        <v>36.233</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.51</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>A round amount (1 of 4 lines); no or vague narration (1 of 4 lines); a manual entry; posted to an account with 3 entries or fewer (1 of 4 lines); a large amount (36 times the median).</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.57</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1278,62 +1314,67 @@
           <t>JV02553</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Suspense Account 29, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45767</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Prepayment release</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Rounded Amount, Sunday, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>110000</v>
       </c>
-      <c r="L8" t="n">
-        <v>35.015</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; a round amount; a manual entry; posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (49 times the median).</t>
-        </is>
+      <c r="M8" t="n">
+        <v>35.74</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.70</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>Posted on a Sunday; a round amount; a manual entry; posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (56 times the median).</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.76</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1344,62 +1385,67 @@
           <t>JV06904</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Suspense Account 15, Accounts Payable, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45877</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Cash advance, no invoice</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>user_a</t>
         </is>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Keyword Match, Manual Entry, Same User Created and Approved, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>12816.14</v>
       </c>
-      <c r="L9" t="n">
-        <v>34.388</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>35.308</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Description matches the keyword list (1 of 3 lines); a manual entry; created and approved by the same user ID; posted to an account with 3 entries or fewer (1 of 3 lines).</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.2 + Seldom Account Entries 7.2 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.83</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Seldom Account Entries 7.2 + Keyword Match 3.6 + Manual Entry 0.8, × amount 1.88</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1410,62 +1456,67 @@
           <t>JV07042</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Suspense Account 4, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45691</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Cash advance, no invoice</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Keyword Match, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>166657.47</v>
       </c>
-      <c r="L10" t="n">
-        <v>31.086</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list (1 of 2 lines); posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (75 times the median).</t>
-        </is>
+      <c r="M10" t="n">
+        <v>31.679</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.2 + Keyword Match 3.6, × amount 2.88</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>Description matches the keyword list (1 of 2 lines); posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (85 times the median).</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + Keyword Match 3.6, × amount 2.94</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1476,62 +1527,67 @@
           <t>JV03333</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Accounts Receivable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45810</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Correction entry - reversal</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>user_b</t>
         </is>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Keyword Match, Rounded Amount, Manual Entry, Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="L11" t="n">
-        <v>30.394</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list (1 of 2 lines); a round amount; a manual entry; created and approved by the same user ID.</t>
-        </is>
+      <c r="M11" t="n">
+        <v>31.169</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2 + Rounded Amount 3.6 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>Description matches the keyword list (1 of 2 lines); a round amount; a manual entry; created and approved by the same user ID; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Rounded Amount 3.6 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1542,62 +1598,67 @@
           <t>JV06563</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Office Supplies, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45913</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Sales invoice</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>user_e</t>
         </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Saturday, Manual Entry, Benford, Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>160513.81</v>
       </c>
-      <c r="L12" t="n">
-        <v>27.716</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Posted on a Saturday; a manual entry; first digit over-represented in this ledger (Benford) (1 of 3 lines); created and approved by the same user ID; a large amount (72 times the median).</t>
-        </is>
+      <c r="M12" t="n">
+        <v>28.248</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2 + date (Saturday) 1.3 + Manual Entry 0.8 + Benford 0.3, × amount 2.87</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>Posted on a Saturday; a manual entry; first digit over-represented in this ledger (Benford) (1 of 3 lines); created and approved by the same user ID; a large amount (82 times the median).</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + date (Saturday) 1.3 + Manual Entry 0.8 + Benford 0.3, × amount 2.92</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1608,62 +1669,67 @@
           <t>JV02549</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suspense Account 20, Accounts Payable, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Adj</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Rounded Amount, No or Vague Narration, Manual Entry, Benford, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>10000</v>
       </c>
-      <c r="L13" t="n">
-        <v>25.145</v>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>25.824</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>A round amount (1 of 4 lines); no or vague narration (1 of 4 lines); a manual entry; first digit over-represented in this ledger (Benford) (2 of 4 lines); posted to an account with 3 entries or fewer (1 of 4 lines).</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8 + Benford 0.3, × amount 1.74</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8 + Benford 0.3, × amount 1.79</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1674,62 +1740,67 @@
           <t>JV01886</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Suspense Account 27, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45852</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Prepayment release</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>20000</v>
       </c>
-      <c r="L14" t="n">
-        <v>23.206</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry; posted to an account with 3 entries or fewer (1 of 2 lines).</t>
-        </is>
+      <c r="M14" t="n">
+        <v>23.798</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>A round amount; a manual entry; posted to an account with 3 entries or fewer (1 of 2 lines); a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1740,62 +1811,67 @@
           <t>JV03821</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Accounts Payable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45703</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Cash advance, no invoice</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>user_c</t>
         </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Keyword Match, Saturday, Manual Entry, Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>11553.68</v>
       </c>
-      <c r="L15" t="n">
-        <v>23.174</v>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>23.795</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Posted on a Saturday; description matches the keyword list (1 of 2 lines); a manual entry; created and approved by the same user ID.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.2 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 1.79</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 1.84</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1806,62 +1882,67 @@
           <t>JV01597</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Accounts Receivable, VAT Payable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Journal entry</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>user_e</t>
         </is>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>No or Vague Narration, Period End, Saturday, Manual Entry, Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>13068.37</v>
       </c>
-      <c r="L16" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>22.349</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Posted near a quarter end and on a Saturday; no or vague narration (1 of 3 lines); a manual entry; created and approved by the same user ID.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Same User Created and Approved 7.2 + No or Vague Narration 2.5 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 1.84</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2 + No or Vague Narration 2.5 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 1.89</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1872,62 +1953,67 @@
           <t>JV03782</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Accounts Payable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45913</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Consultancy fee (related party)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Keyword Match, Ending 99/999, Saturday, Manual Entry</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>22999</v>
       </c>
-      <c r="L17" t="n">
-        <v>20.959</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Posted on a Saturday; description matches the keyword list (1 of 2 lines); an amount ending in 99 or 999; a manual entry; a large amount (10 times the median).</t>
-        </is>
+      <c r="M17" t="n">
+        <v>21.489</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.5 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 2.06</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Posted on a Saturday; description matches the keyword list (1 of 2 lines); an amount ending in 99 or 999; a manual entry; a large amount (12 times the median).</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.5 + Keyword Match 3.6 + date (Saturday) 1.3 + Manual Entry 0.8, × amount 2.11</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1938,62 +2024,67 @@
           <t>JV02184</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Utilities, Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45673</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Adjustment per director</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H18" t="n">
-        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Keyword Match, Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>60000</v>
       </c>
-      <c r="L18" t="n">
-        <v>19.578</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list (1 of 4 lines); a round amount (1 of 4 lines); a manual entry; a large amount (27 times the median).</t>
-        </is>
+      <c r="M18" t="n">
+        <v>20.019</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.45</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>Description matches the keyword list (1 of 4 lines); a round amount (1 of 4 lines); a manual entry; a large amount (31 times the median).</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Keyword Match 3.6 + Manual Entry 0.8, × amount 2.50</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2004,62 +2095,67 @@
           <t>JV00292</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Utilities, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45931</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>JV</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Rounded Amount, No or Vague Narration, Period End, Manual Entry</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>50000</v>
       </c>
-      <c r="L19" t="n">
-        <v>18.885</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Posted near a quarter end; a round amount; no or vague narration (1 of 2 lines); a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M19" t="n">
+        <v>19.315</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>Posted near a quarter end; a round amount; no or vague narration (1 of 2 lines); a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2070,62 +2166,67 @@
           <t>JV02940</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Cash advance, no invoice</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Keyword Match, Rounded Amount, Sunday, Manual Entry</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>20000</v>
       </c>
-      <c r="L20" t="n">
-        <v>18.704</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; description matches the keyword list (1 of 2 lines); a round amount; a manual entry.</t>
-        </is>
+      <c r="M20" t="n">
+        <v>19.181</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>Posted on a Sunday; description matches the keyword list (1 of 2 lines); a round amount; a manual entry; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2136,62 +2237,67 @@
           <t>JV01314</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Payroll Expense, Cash at Bank, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>45664</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Monthly payroll</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H21" t="n">
-        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Ending 99/999, Period End, Manual Entry</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>134999</v>
       </c>
-      <c r="L21" t="n">
-        <v>17.622</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Posted just after the prior year-end; an amount ending in 99 or 999 (1 of 3 lines); a manual entry; a large amount (61 times the median).</t>
-        </is>
+      <c r="M21" t="n">
+        <v>17.97</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.5 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.79</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>Posted just after the prior year-end; an amount ending in 99 or 999 (1 of 3 lines); a manual entry; a large amount (69 times the median).</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.5 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.85</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2202,62 +2308,67 @@
           <t>JV00221</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Suspense Account 7, Accounts Receivable, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Utility bill</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Saturday, Manual Entry, Benford, Seldom Account Entries</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>11884.51</v>
       </c>
-      <c r="L22" t="n">
-        <v>17.442</v>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>17.907</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Posted on a Saturday; a manual entry; first digit over-represented in this ledger (Benford) (1 of 4 lines); posted to an account with 3 entries or fewer (1 of 4 lines).</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Seldom Account Entries 7.2 + date (Saturday) 1.3 + Manual Entry 0.8 + Benford 0.3, × amount 1.80</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Seldom Account Entries 7.2 + date (Saturday) 1.3 + Manual Entry 0.8 + Benford 0.3, × amount 1.85</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2268,62 +2379,67 @@
           <t>JV02843</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Accounts Receivable, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45797</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Rounded Amount, No or Vague Narration, Manual Entry</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>50000</v>
       </c>
-      <c r="L23" t="n">
-        <v>16.405</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A round amount; no or vague narration (1 of 2 lines); a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M23" t="n">
+        <v>16.779</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>A round amount; no or vague narration (1 of 2 lines); a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2334,62 +2450,67 @@
           <t>JV02442</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Accounts Payable, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45856</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Supplier payment</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>user_b</t>
         </is>
-      </c>
-      <c r="H24" t="n">
-        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Same User Created and Approved</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>34434.29</v>
       </c>
-      <c r="L24" t="n">
-        <v>15.954</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Created and approved by the same user ID; a large amount (15 times the median).</t>
-        </is>
+      <c r="M24" t="n">
+        <v>16.335</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Same User Created and Approved 7.2, × amount 2.22</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Created and approved by the same user ID; a large amount (18 times the median).</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Same User Created and Approved 7.2, × amount 2.27</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2400,62 +2521,67 @@
           <t>JV00521</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>45743</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>104522</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Rounded Amount, No or Vague Narration, Manual Entry</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>30000</v>
       </c>
-      <c r="L25" t="n">
-        <v>14.952</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A round amount; no or vague narration (1 of 2 lines); a manual entry; a large amount (13 times the median).</t>
-        </is>
+      <c r="M25" t="n">
+        <v>15.319</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.16</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>A round amount; no or vague narration (1 of 2 lines); a manual entry; a large amount (15 times the median).</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 2.21</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2466,62 +2592,67 @@
           <t>JV07312</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cost of Sales, Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Purchase invoice</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H26" t="n">
-        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Rounded Amount, Sunday, Manual Entry</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>60000</v>
       </c>
-      <c r="L26" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; a round amount (1 of 3 lines); a manual entry; a large amount (27 times the median).</t>
-        </is>
+      <c r="M26" t="n">
+        <v>14.407</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.45</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>Posted on a Sunday; a round amount (1 of 3 lines); a manual entry; a large amount (31 times the median).</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2532,62 +2663,67 @@
           <t>JV06521</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>45798</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Prepayment release</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Ending 99/999, Manual Entry, Benford</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>48999</v>
       </c>
-      <c r="L27" t="n">
-        <v>13.242</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>An amount ending in 99 or 999; a manual entry; first digit over-represented in this ledger (Benford); a large amount (22 times the median).</t>
-        </is>
+      <c r="M27" t="n">
+        <v>13.545</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.5 + Manual Entry 0.8 + Benford 0.3, × amount 2.36</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>An amount ending in 99 or 999; a manual entry; first digit over-represented in this ledger (Benford); a large amount (25 times the median).</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.5 + Manual Entry 0.8 + Benford 0.3, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2598,62 +2734,67 @@
           <t>JV00906</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Accounts Payable, VAT Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Utility bill</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>user_d</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H28" t="n">
-        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>3</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Rounded Amount, Period End, Manual Entry</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>50000</v>
       </c>
-      <c r="L28" t="n">
-        <v>12.929</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; a round amount (1 of 3 lines); a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M28" t="n">
+        <v>13.224</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>Posted near the year-end; a round amount (1 of 3 lines); a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + date (Period End) 1.0 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2661,65 +2802,70 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JV05095</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>45661</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Write off - settlement</t>
-        </is>
+          <t>JV03179</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Accounts Payable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45690</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>manager_2</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
+          <t>user_e</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>manager_1</t>
+        </is>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Keyword Match, Period End</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>120977.01</v>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ending 99/999, Sunday, Manual Entry</t>
+        </is>
       </c>
       <c r="L29" t="n">
-        <v>12.732</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Posted just after the prior year-end; description matches the keyword list (1 of 2 lines); a large amount (54 times the median).</t>
-        </is>
+        <v>15999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>13</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + date (Period End) 1.0, × amount 2.74</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Posted on a Sunday; an amount ending in 99 or 999; a manual entry.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.5 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 1.96</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2727,65 +2873,70 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JV03179</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>45690</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Staff travel claim</t>
-        </is>
+          <t>JV05095</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rent Expense, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45661</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>manager_1</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
+          <t>user_c</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>manager_2</t>
+        </is>
       </c>
       <c r="I30" t="n">
         <v>2</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Ending 99/999, Sunday, Manual Entry</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>15999</v>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Keyword Match, Period End</t>
+        </is>
       </c>
       <c r="L30" t="n">
-        <v>12.669</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; an amount ending in 99 or 999; a manual entry.</t>
-        </is>
+        <v>120977.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12.987</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.5 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 1.91</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>Posted just after the prior year-end; description matches the keyword list (1 of 2 lines); a large amount (62 times the median).</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Period End) 1.0, × amount 2.80</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2796,62 +2947,67 @@
           <t>JV06352</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Payroll Expense, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>45681</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Journal entry</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H31" t="n">
-        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Rounded Amount, No or Vague Narration, Manual Entry</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>10000</v>
       </c>
-      <c r="L31" t="n">
-        <v>12.039</v>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>12.364</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>A round amount; no or vague narration (1 of 2 lines); a manual entry.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 1.74</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + No or Vague Narration 2.5 + Manual Entry 0.8, × amount 1.79</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2862,62 +3018,67 @@
           <t>JV04573</t>
         </is>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Utilities, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Correction entry - reversal</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H32" t="n">
-        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Keyword Match, Sunday, Manual Entry</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>24069.39</v>
       </c>
-      <c r="L32" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; description matches the keyword list (1 of 4 lines); a manual entry; a large amount (11 times the median).</t>
-        </is>
+      <c r="M32" t="n">
+        <v>12.219</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.07</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>Posted on a Sunday; description matches the keyword list (1 of 4 lines); a manual entry; a large amount (12 times the median).</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.12</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2928,62 +3089,67 @@
           <t>JV02276</t>
         </is>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>45792</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Correction entry - reversal</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>2</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Keyword Match, Manual Entry</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>109801.41</v>
       </c>
-      <c r="L33" t="n">
-        <v>11.886</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list (1 of 2 lines); a manual entry; a large amount (49 times the median).</t>
-        </is>
+      <c r="M33" t="n">
+        <v>12.132</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + Manual Entry 0.8, × amount 2.70</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>Description matches the keyword list (1 of 2 lines); a manual entry; a large amount (56 times the median).</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + Manual Entry 0.8, × amount 2.76</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2994,62 +3160,67 @@
           <t>JV05949</t>
         </is>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>45772</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Monthly payroll</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H34" t="n">
-        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>2</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>90000</v>
       </c>
-      <c r="L34" t="n">
-        <v>11.538</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry; a large amount (40 times the median).</t>
-        </is>
+      <c r="M34" t="n">
+        <v>11.78</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.62</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>A round amount; a manual entry; a large amount (46 times the median).</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.67</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3060,62 +3231,67 @@
           <t>JV03630</t>
         </is>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cash at Bank, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>46021</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Director fees</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H35" t="n">
-        <v>4</v>
       </c>
       <c r="I35" t="n">
         <v>4</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Keyword Match, Period End</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>50000</v>
       </c>
-      <c r="L35" t="n">
-        <v>11.001</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Posted near the year-end; description matches the keyword list; a large amount (22 times the median).</t>
-        </is>
+      <c r="M35" t="n">
+        <v>11.252</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + date (Period End) 1.0, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>Posted near the year-end; description matches the keyword list; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Period End) 1.0, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3126,62 +3302,67 @@
           <t>JV06572</t>
         </is>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Revenue, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Staff travel claim</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H36" t="n">
-        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>2</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>60000</v>
       </c>
-      <c r="L36" t="n">
-        <v>10.784</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry; a large amount (27 times the median).</t>
-        </is>
+      <c r="M36" t="n">
+        <v>11.026</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.45</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>A round amount; a manual entry; a large amount (31 times the median).</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.50</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3192,62 +3373,67 @@
           <t>JV05127</t>
         </is>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Accounts Receivable, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>45868</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Bank charges</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H37" t="n">
-        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Ending 99/999, Manual Entry</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>21999</v>
       </c>
-      <c r="L37" t="n">
-        <v>10.731</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>An amount ending in 99 or 999; a manual entry.</t>
-        </is>
+      <c r="M37" t="n">
+        <v>11.005</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.5 + Manual Entry 0.8, × amount 2.04</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>An amount ending in 99 or 999; a manual entry; a large amount (11 times the median).</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.5 + Manual Entry 0.8, × amount 2.09</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3258,62 +3444,67 @@
           <t>JV02872</t>
         </is>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Accounts Payable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>45903</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Director fees</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H38" t="n">
-        <v>2</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Keyword Match</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>189943.48</v>
       </c>
-      <c r="L38" t="n">
-        <v>10.556</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a large amount (85 times the median).</t>
-        </is>
+      <c r="M38" t="n">
+        <v>10.757</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6, × amount 2.94</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>Description matches the keyword list; a large amount (97 times the median).</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6, × amount 2.99</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3324,62 +3515,67 @@
           <t>JV03722</t>
         </is>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Accounts Payable, VAT Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>45791</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Sales invoice</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H39" t="n">
-        <v>3</v>
       </c>
       <c r="I39" t="n">
         <v>3</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>50000</v>
       </c>
-      <c r="L39" t="n">
-        <v>10.449</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 3 lines); a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M39" t="n">
+        <v>10.687</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>A round amount (1 of 3 lines); a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3390,62 +3586,67 @@
           <t>JV04913</t>
         </is>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cost of Sales, Accounts Payable, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
         <v>45824</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Sales invoice</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>user_d</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H40" t="n">
-        <v>4</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>50000</v>
       </c>
-      <c r="L40" t="n">
-        <v>10.449</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 4 lines); a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M40" t="n">
+        <v>10.687</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+          <t>A round amount (1 of 4 lines); a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3456,62 +3657,67 @@
           <t>JV00968</t>
         </is>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Accounts Receivable, Cash at Bank, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Sales invoice</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H41" t="n">
-        <v>4</v>
       </c>
       <c r="I41" t="n">
         <v>4</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>50000</v>
       </c>
-      <c r="L41" t="n">
-        <v>10.449</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 4 lines); a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M41" t="n">
+        <v>10.687</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>A round amount (1 of 4 lines); a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3522,62 +3728,67 @@
           <t>JV01199</t>
         </is>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Payroll Expense, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
         <v>46014</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Purchase invoice</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>50000</v>
       </c>
-      <c r="L42" t="n">
-        <v>10.449</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry; a large amount (22 times the median).</t>
-        </is>
+      <c r="M42" t="n">
+        <v>10.687</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.37</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>A round amount; a manual entry; a large amount (26 times the median).</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.42</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3588,62 +3799,67 @@
           <t>JV02134</t>
         </is>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rent Expense, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H43" t="n">
-        <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>No or Vague Narration, Sunday, Manual Entry</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>28025.15</v>
       </c>
-      <c r="L43" t="n">
-        <v>9.962</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Posted on a Sunday; no or vague narration (1 of 2 lines); a manual entry; a large amount (13 times the median).</t>
-        </is>
+      <c r="M43" t="n">
+        <v>10.204</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>No or Vague Narration 2.5 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.13</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>Posted on a Sunday; no or vague narration (1 of 2 lines); a manual entry; a large amount (14 times the median).</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>No or Vague Narration 2.5 + date (Sunday) 1.4 + Manual Entry 0.8, × amount 2.19</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3654,62 +3870,67 @@
           <t>JV03543</t>
         </is>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cost of Sales, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
         <v>45658</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Director fees</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H44" t="n">
-        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Keyword Match, Period End</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>25033.56</v>
       </c>
-      <c r="L44" t="n">
-        <v>9.693</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Posted just after the prior year-end; description matches the keyword list; a large amount (11 times the median).</t>
-        </is>
+      <c r="M44" t="n">
+        <v>9.933999999999999</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + date (Period End) 1.0, × amount 2.09</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>Posted just after the prior year-end; description matches the keyword list; a large amount (13 times the median).</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + date (Period End) 1.0, × amount 2.14</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3720,62 +3941,67 @@
           <t>JV02670</t>
         </is>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Accounts Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>45832</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Prepayment release</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>user_a</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H45" t="n">
-        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>3</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry, Benford</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>20000</v>
       </c>
-      <c r="L45" t="n">
-        <v>9.486000000000001</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 3 lines); a manual entry; first digit over-represented in this ledger (Benford) (1 of 3 lines).</t>
-        </is>
+      <c r="M45" t="n">
+        <v>9.728</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8 + Benford 0.3, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>A round amount (1 of 3 lines); a manual entry; first digit over-represented in this ledger (Benford) (1 of 3 lines); a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8 + Benford 0.3, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3786,62 +4012,67 @@
           <t>JV00749</t>
         </is>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cost of Sales, Accounts Payable, VAT Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
         <v>46009</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Director fees</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>user_d</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H46" t="n">
-        <v>4</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Keyword Match, Benford</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>48076.28</v>
       </c>
-      <c r="L46" t="n">
-        <v>9.255000000000001</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; first digit over-represented in this ledger (Benford) (1 of 4 lines); a large amount (22 times the median).</t>
-        </is>
+      <c r="M46" t="n">
+        <v>9.467000000000001</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + Benford 0.3, × amount 2.35</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
+          <t>Description matches the keyword list; first digit over-represented in this ledger (Benford) (1 of 4 lines); a large amount (25 times the median).</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + Benford 0.3, × amount 2.41</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3852,62 +4083,67 @@
           <t>JV00984</t>
         </is>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Accounts Payable, Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
         <v>45827</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Director fees</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>user_e</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H47" t="n">
-        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Keyword Match, Manual Entry</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>25698.59</v>
       </c>
-      <c r="L47" t="n">
-        <v>9.234</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Description matches the keyword list; a manual entry; a large amount (12 times the median).</t>
-        </is>
+      <c r="M47" t="n">
+        <v>9.462</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Keyword Match 3.6 + Manual Entry 0.8, × amount 2.10</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+          <t>Description matches the keyword list; a manual entry; a large amount (13 times the median).</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Keyword Match 3.6 + Manual Entry 0.8, × amount 2.15</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3918,62 +4154,67 @@
           <t>JV01833</t>
         </is>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cost of Sales, Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
         <v>45848</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Accrual</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>user_d</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H48" t="n">
-        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Ending 99/999</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>19999</v>
       </c>
-      <c r="L48" t="n">
-        <v>8.926</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>An amount ending in 99 or 999.</t>
-        </is>
+      <c r="M48" t="n">
+        <v>9.154</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Ending 99/999 4.5, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>An amount ending in 99 or 999; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Ending 99/999 4.5, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3984,62 +4225,67 @@
           <t>JV05465</t>
         </is>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cost of Sales, VAT Payable, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Staff travel claim</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H49" t="n">
-        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>20000</v>
       </c>
-      <c r="L49" t="n">
-        <v>8.814</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 3 lines); a manual entry.</t>
-        </is>
+      <c r="M49" t="n">
+        <v>9.039</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>A round amount (1 of 3 lines); a manual entry; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4050,62 +4296,67 @@
           <t>JV05326</t>
         </is>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Revenue, VAT Payable</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
         <v>45796</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Prepayment release</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>user_c</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>manager_1</t>
         </is>
-      </c>
-      <c r="H50" t="n">
-        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>20000</v>
       </c>
-      <c r="L50" t="n">
-        <v>8.814</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>A round amount; a manual entry.</t>
-        </is>
+      <c r="M50" t="n">
+        <v>9.039</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>A round amount; a manual entry; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4116,65 +4367,70 @@
           <t>JV06121</t>
         </is>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cash at Bank, VAT Payable, Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
         <v>45880</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Supplier payment</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>user_b</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>manager_2</t>
         </is>
-      </c>
-      <c r="H51" t="n">
-        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>3</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Rounded Amount, Manual Entry</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>20000</v>
       </c>
-      <c r="L51" t="n">
-        <v>8.814</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>A round amount (1 of 3 lines); a manual entry.</t>
-        </is>
+      <c r="M51" t="n">
+        <v>9.039</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.00</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>A round amount (1 of 3 lines); a manual entry; a large amount (10 times the median).</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Rounded Amount 3.6 + Manual Entry 0.8, × amount 2.05</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T51"/>
+  <autoFilter ref="A1:U51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9156,48 +9412,48 @@
         <v>28</v>
       </c>
       <c r="B75" t="n">
-        <v>248</v>
+        <v>1817</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45661</v>
+        <v>45690</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>JV05095</t>
+          <t>JV03179</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rent Expense</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>120977.01</v>
+        <v>15999</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -9209,39 +9465,31 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Keyword Match, Period End</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Opening cut-off</t>
-        </is>
-      </c>
+          <t>Ending 99/999, Sunday, Manual Entry</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>settlement, write off</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>28</v>
       </c>
       <c r="B76" t="n">
-        <v>249</v>
+        <v>1818</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45661</v>
+        <v>45690</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JV05095</t>
+          <t>JV03179</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>VAT Payable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9251,29 +9499,29 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>120977.01</v>
+        <v>15999</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9282,14 +9530,10 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Period End</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Opening cut-off</t>
-        </is>
-      </c>
+          <t>Ending 99/999, Sunday, Manual Entry</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
     </row>
@@ -9298,48 +9542,48 @@
         <v>29</v>
       </c>
       <c r="B77" t="n">
-        <v>1817</v>
+        <v>248</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45690</v>
+        <v>45661</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JV03179</t>
+          <t>JV05095</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Rent Expense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>15999</v>
+        <v>120977.01</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -9351,31 +9595,39 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Ending 99/999, Sunday, Manual Entry</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
+          <t>Keyword Match, Period End</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>settlement, write off</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>29</v>
       </c>
       <c r="B78" t="n">
-        <v>1818</v>
+        <v>249</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45690</v>
+        <v>45661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JV03179</t>
+          <t>JV05095</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>VAT Payable</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9385,29 +9637,29 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>System</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>15999</v>
+        <v>120977.01</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9416,10 +9668,14 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Ending 99/999, Sunday, Manual Entry</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Opening cut-off</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
     </row>
@@ -13207,7 +13463,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amount multiplier = 1 + log10(1 + voucher amount / median); voucher amount = larger of total debits and credits; median 2,222.42.</t>
+          <t>Amount multiplier = 1 + log10(1 + voucher amount / median); voucher amount = larger of total debits and credits; median 1,952.05.</t>
         </is>
       </c>
     </row>
